--- a/evac_by_zip/evac_by_zip_2026-08-28.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-28.xlsx
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 223 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 228 addresses (across 1 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -641,13 +641,13 @@
         <v>45</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -802,138 +802,144 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>No named fire</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>99362</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="n">
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
@@ -942,11 +948,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>97814</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -954,10 +960,10 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -966,122 +972,120 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="E15" s="7" t="n">
+        <v>231</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="E16" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
@@ -1090,14 +1094,14 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>225</v>
+        <v>22</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -1105,7 +1109,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1114,12 +1118,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
@@ -1431,13 +1435,13 @@
         <v>1454</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>916</v>
+        <v>975</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>2492</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="28">
@@ -1450,13 +1454,13 @@
         <v>167</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29">
@@ -1469,10 +1473,10 @@
         <v>1621</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>941</v>
+        <v>1006</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="E29" s="18" t="n">
         <v>2715</v>
@@ -1493,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1557,7 +1561,7 @@
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
+          <t>US-OR-UMA-UMC-243</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -1581,7 +1585,7 @@
         </is>
       </c>
       <c r="G3" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-UNI-UCO-140618N</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
@@ -1612,81 +1616,81 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G4" s="21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>97886</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-243</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-119-B</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G5" s="21" t="n">
-        <v>1</v>
+      <c r="G5" s="23" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>97886</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-155-A</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>1</v>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -1697,7 +1701,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-119-B</t>
+          <t>US-OR-UMA-UMC-123-F</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -1721,7 +1725,7 @@
         </is>
       </c>
       <c r="G7" s="23" t="n">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-155-A</t>
+          <t>US-OR-UMA-UMC-1406020-B</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -1756,7 +1760,7 @@
         </is>
       </c>
       <c r="G8" s="23" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1767,7 +1771,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-F</t>
+          <t>US-OR-UMA-UMC-123-D</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -1791,7 +1795,7 @@
         </is>
       </c>
       <c r="G9" s="23" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -1802,7 +1806,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406020-B</t>
+          <t>US-OR-UMA-UMC-157-A</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -1826,7 +1830,7 @@
         </is>
       </c>
       <c r="G10" s="23" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1837,7 +1841,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-D</t>
+          <t>US-OR-UMA-UMC-121-A</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -1861,7 +1865,7 @@
         </is>
       </c>
       <c r="G11" s="23" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -1872,7 +1876,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-157-A</t>
+          <t>US-OR-UMA-UMC-123-E</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -1896,7 +1900,7 @@
         </is>
       </c>
       <c r="G12" s="23" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -1907,7 +1911,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-121-A</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -1931,7 +1935,7 @@
         </is>
       </c>
       <c r="G13" s="23" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1942,7 +1946,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-E</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -1962,11 +1966,11 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1977,7 +1981,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -2001,7 +2005,7 @@
         </is>
       </c>
       <c r="G15" s="23" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2012,7 +2016,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UMA-UMC-1406017-A</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -2032,11 +2036,11 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G16" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -5087,22 +5091,22 @@
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-KLA-KLA-1713-B</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E104" s="21" t="inlineStr">
@@ -5112,32 +5116,32 @@
       </c>
       <c r="F104" s="21" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G104" s="21" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="21" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B105" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
+          <t>US-OR-KLA-KLA-1713-A</t>
         </is>
       </c>
       <c r="C105" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D105" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E105" s="21" t="inlineStr">
@@ -5147,102 +5151,102 @@
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G105" s="21" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="21" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-A</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D106" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G106" s="21" t="n">
+      <c r="A106" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1707</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C107" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E107" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B107" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
-        </is>
-      </c>
-      <c r="C107" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D107" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E107" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F107" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G107" s="21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="23" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-E</t>
+          <t>US-OR-KLA-KLA-1956</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
@@ -5252,197 +5256,197 @@
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B109" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-215-E</t>
-        </is>
-      </c>
-      <c r="C109" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D109" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E109" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F109" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="n">
-        <v>9</v>
+      <c r="A109" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B109" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C109" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D109" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E109" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F109" s="25" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G109" s="25" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B110" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-215-D</t>
-        </is>
-      </c>
-      <c r="C110" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D110" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E110" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F110" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G110" s="23" t="n">
-        <v>7</v>
+      <c r="A110" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B110" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1946</t>
+        </is>
+      </c>
+      <c r="C110" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D110" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E110" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F110" s="25" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G110" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B111" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-151-D</t>
-        </is>
-      </c>
-      <c r="C111" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D111" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E111" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F111" s="23" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="n">
-        <v>6</v>
+      <c r="A111" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B111" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1701</t>
+        </is>
+      </c>
+      <c r="C111" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D111" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E111" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F111" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G111" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B112" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-153</t>
-        </is>
-      </c>
-      <c r="C112" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D112" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E112" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F112" s="23" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="n">
-        <v>6</v>
+      <c r="A112" s="25" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B112" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1361</t>
+        </is>
+      </c>
+      <c r="C112" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D112" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E112" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F112" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G112" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C113" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D113" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E113" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F113" s="23" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="G113" s="23" t="n">
-        <v>5</v>
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E113" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="23" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UNI-UCO-140624N-B</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
@@ -5452,7 +5456,7 @@
       </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
@@ -5462,22 +5466,22 @@
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="23" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-149-B</t>
+          <t>US-OR-UNI-UCO-140624S</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
@@ -5487,7 +5491,7 @@
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
@@ -5497,7 +5501,7 @@
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="G115" s="23" t="n">
@@ -5507,12 +5511,12 @@
     <row r="116">
       <c r="A116" s="23" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-155-B</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
@@ -5522,7 +5526,7 @@
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -5532,7 +5536,7 @@
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G116" s="23" t="n">
@@ -5540,49 +5544,49 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="25" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B117" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-215-C</t>
-        </is>
-      </c>
-      <c r="C117" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D117" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E117" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F117" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G117" s="25" t="n">
-        <v>11</v>
+      <c r="A117" s="23" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406024A</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E117" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B118" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-F</t>
+          <t>US-OR-UNI-UCO-1497</t>
         </is>
       </c>
       <c r="C118" s="26" t="inlineStr">
@@ -5592,7 +5596,7 @@
       </c>
       <c r="D118" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E118" s="25" t="inlineStr">
@@ -5602,22 +5606,22 @@
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G118" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="25" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B119" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-G</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C119" s="26" t="inlineStr">
@@ -5627,7 +5631,7 @@
       </c>
       <c r="D119" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
@@ -5637,7 +5641,7 @@
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G119" s="25" t="n">
@@ -5645,129 +5649,129 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="21" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C120" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D120" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E120" s="21" t="inlineStr">
+      <c r="A120" s="25" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B120" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1513</t>
+        </is>
+      </c>
+      <c r="C120" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D120" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E120" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F120" s="25" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G120" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="25" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B121" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1495</t>
+        </is>
+      </c>
+      <c r="C121" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D121" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E121" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F121" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G121" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="21" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1119-B</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E122" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F120" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G120" s="21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="23" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B121" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C121" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D121" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E121" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G121" s="23" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B122" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C122" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D122" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E122" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F122" s="25" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G122" s="25" t="n">
-        <v>22</v>
+      <c r="F122" s="21" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G122" s="21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="21" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B123" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
+          <t>US-OR-BAK-BAB-1247</t>
         </is>
       </c>
       <c r="C123" s="22" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5777,7 +5781,7 @@
       </c>
       <c r="F123" s="21" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G123" s="21" t="n">
@@ -5787,22 +5791,22 @@
     <row r="124">
       <c r="A124" s="21" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
+          <t>US-OR-BAK-BAB-1246</t>
         </is>
       </c>
       <c r="C124" s="22" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D124" s="22" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E124" s="21" t="inlineStr">
@@ -5812,7 +5816,7 @@
       </c>
       <c r="F124" s="21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G124" s="21" t="n">
@@ -5822,22 +5826,22 @@
     <row r="125">
       <c r="A125" s="23" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1707</t>
+          <t>US-OR-BAK-SMT-636</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D125" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
@@ -5847,102 +5851,102 @@
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G125" s="23" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B126" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C126" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D126" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E126" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F126" s="23" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="G126" s="23" t="n">
-        <v>4</v>
+      <c r="A126" s="25" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B126" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1252</t>
+        </is>
+      </c>
+      <c r="C126" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D126" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E126" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F126" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G126" s="25" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1956</t>
-        </is>
-      </c>
-      <c r="C127" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D127" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E127" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F127" s="23" t="inlineStr">
+      <c r="A127" s="25" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B127" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-610</t>
+        </is>
+      </c>
+      <c r="C127" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D127" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E127" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F127" s="25" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G127" s="23" t="n">
+      <c r="G127" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B128" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-BAK-SMT-600</t>
         </is>
       </c>
       <c r="C128" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D128" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E128" s="25" t="inlineStr">
@@ -5952,32 +5956,32 @@
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G128" s="25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B129" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1946</t>
+          <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D129" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -5987,67 +5991,67 @@
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G129" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="25" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B130" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1701</t>
-        </is>
-      </c>
-      <c r="C130" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D130" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E130" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F130" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G130" s="25" t="n">
+      <c r="A130" s="21" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1119-B</t>
+        </is>
+      </c>
+      <c r="C130" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E130" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97833</t>
         </is>
       </c>
       <c r="B131" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1361</t>
+          <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
       <c r="C131" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D131" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -6057,67 +6061,67 @@
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="G131" s="25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="25" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B132" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1252</t>
+        </is>
+      </c>
+      <c r="C132" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D132" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E132" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F132" s="25" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G131" s="25" t="n">
+      <c r="G132" s="25" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B132" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C132" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D132" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E132" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F132" s="21" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G132" s="21" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="21" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B133" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624S</t>
+          <t>NF 27</t>
         </is>
       </c>
       <c r="C133" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D133" s="22" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E133" s="21" t="inlineStr">
@@ -6127,137 +6131,137 @@
       </c>
       <c r="F133" s="21" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G133" s="21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="25" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B134" s="26" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="C134" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D134" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E134" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F134" s="25" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="G134" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B134" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C134" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D134" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E134" s="21" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B135" s="22" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E135" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F134" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G134" s="21" t="n">
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G135" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="23" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B135" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
-        </is>
-      </c>
-      <c r="C135" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D135" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E135" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F135" s="23" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>5</v>
-      </c>
-    </row>
     <row r="136">
-      <c r="A136" s="23" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B136" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
-        </is>
-      </c>
-      <c r="C136" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D136" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E136" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F136" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G136" s="23" t="n">
+      <c r="A136" s="21" t="inlineStr">
+        <is>
+          <t>97063</t>
+        </is>
+      </c>
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E136" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F136" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G136" s="21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="25" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="B137" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1497</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D137" s="26" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -6267,7 +6271,7 @@
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G137" s="25" t="n">
@@ -6275,864 +6279,864 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B138" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1505</t>
-        </is>
-      </c>
-      <c r="C138" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D138" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E138" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F138" s="25" t="inlineStr">
+      <c r="A138" s="21" t="inlineStr">
+        <is>
+          <t>97358</t>
+        </is>
+      </c>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C138" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E138" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F138" s="21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G138" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D139" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E139" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F139" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>Mill Creek Buttes</t>
+        </is>
+      </c>
+      <c r="C140" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D140" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E140" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F140" s="23" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G140" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B141" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D141" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E141" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F141" s="25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G141" s="25" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B142" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur South</t>
+        </is>
+      </c>
+      <c r="C142" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D142" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E142" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F142" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G142" s="25" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B143" s="26" t="inlineStr">
+        <is>
+          <t>Gibson Prairie</t>
+        </is>
+      </c>
+      <c r="C143" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D143" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E143" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F143" s="25" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G143" s="25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B144" s="26" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="C144" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D144" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E144" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F144" s="25" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="G144" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406017-A</t>
+        </is>
+      </c>
+      <c r="C145" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D145" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E145" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F145" s="23" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B146" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406053-C</t>
+        </is>
+      </c>
+      <c r="C146" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D146" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E146" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F146" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-E</t>
+        </is>
+      </c>
+      <c r="C147" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D147" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E147" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F147" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B148" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-E</t>
+        </is>
+      </c>
+      <c r="C148" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D148" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E148" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F148" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B149" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-D</t>
+        </is>
+      </c>
+      <c r="C149" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D149" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E149" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F149" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G149" s="23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B150" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-151-D</t>
+        </is>
+      </c>
+      <c r="C150" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D150" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E150" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F150" s="23" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
       </c>
-      <c r="G138" s="25" t="n">
+      <c r="G150" s="23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B151" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-153</t>
+        </is>
+      </c>
+      <c r="C151" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D151" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E151" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F151" s="23" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B152" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C152" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D152" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E152" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F152" s="23" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B153" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-C</t>
+        </is>
+      </c>
+      <c r="C153" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D153" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E153" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F153" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B154" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-149-B</t>
+        </is>
+      </c>
+      <c r="C154" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D154" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E154" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F154" s="23" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G154" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B139" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1513</t>
-        </is>
-      </c>
-      <c r="C139" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D139" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E139" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F139" s="25" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G139" s="25" t="n">
+    <row r="155">
+      <c r="A155" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406053-B</t>
+        </is>
+      </c>
+      <c r="C155" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D155" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E155" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B140" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1495</t>
-        </is>
-      </c>
-      <c r="C140" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D140" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E140" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F140" s="25" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B156" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-155-B</t>
+        </is>
+      </c>
+      <c r="C156" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D156" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E156" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F156" s="23" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G156" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B157" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-C</t>
+        </is>
+      </c>
+      <c r="C157" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D157" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E157" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F157" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G157" s="25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B158" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-F</t>
+        </is>
+      </c>
+      <c r="C158" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D158" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E158" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F158" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G158" s="25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="25" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B159" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-151-G</t>
+        </is>
+      </c>
+      <c r="C159" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D159" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E159" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F159" s="25" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G140" s="25" t="n">
+      <c r="G159" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B141" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1119-B</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D141" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E141" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F141" s="21" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G141" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B142" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1247</t>
-        </is>
-      </c>
-      <c r="C142" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D142" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E142" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F142" s="21" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G142" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B143" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C143" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D143" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E143" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F143" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G143" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="23" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B144" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-636</t>
-        </is>
-      </c>
-      <c r="C144" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D144" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E144" s="23" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="23" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C160" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D160" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E160" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F144" s="23" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G144" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B145" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1252</t>
-        </is>
-      </c>
-      <c r="C145" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D145" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E145" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F145" s="25" t="inlineStr">
+      <c r="F160" s="23" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="23" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406043-C</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D161" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E161" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F161" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G145" s="25" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B146" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-610</t>
-        </is>
-      </c>
-      <c r="C146" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D146" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E146" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F146" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G146" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B147" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-600</t>
-        </is>
-      </c>
-      <c r="C147" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D147" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E147" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F147" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G147" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B148" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1242</t>
-        </is>
-      </c>
-      <c r="C148" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D148" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E148" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F148" s="25" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G148" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="21" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B149" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1119-B</t>
-        </is>
-      </c>
-      <c r="C149" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D149" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E149" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F149" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G149" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="25" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B150" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1242</t>
-        </is>
-      </c>
-      <c r="C150" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D150" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E150" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F150" s="25" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="G150" s="25" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="25" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B151" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1252</t>
-        </is>
-      </c>
-      <c r="C151" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D151" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E151" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F151" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G151" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="21" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B152" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C152" s="22" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D152" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E152" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F152" s="21" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G152" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="25" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B153" s="26" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C153" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D153" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E153" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F153" s="25" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="G153" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B154" s="22" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C154" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D154" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E154" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F154" s="21" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G154" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="21" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="B155" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C155" s="22" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D155" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E155" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F155" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G155" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="25" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="B156" s="26" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
-      <c r="C156" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D156" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E156" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F156" s="25" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G156" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="21" t="inlineStr">
-        <is>
-          <t>97358</t>
-        </is>
-      </c>
-      <c r="B157" s="22" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C157" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D157" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E157" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F157" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G157" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B158" s="24" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C158" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D158" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E158" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F158" s="23" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="n">
+      <c r="G161" s="23" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B159" s="24" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C159" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D159" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E159" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F159" s="23" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B160" s="26" t="inlineStr">
-        <is>
-          <t>Cooper Spur North</t>
-        </is>
-      </c>
-      <c r="C160" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D160" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E160" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F160" s="25" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="G160" s="25" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B161" s="26" t="inlineStr">
-        <is>
-          <t>Cooper Spur South</t>
-        </is>
-      </c>
-      <c r="C161" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D161" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E161" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F161" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G161" s="25" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="25" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="B162" s="26" t="inlineStr">
         <is>
-          <t>Gibson Prairie</t>
+          <t>US-OR-UMA-UMC-032</t>
         </is>
       </c>
       <c r="C162" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D162" s="26" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E162" s="25" t="inlineStr">
@@ -7142,46 +7146,46 @@
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="G162" s="25" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B163" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C163" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D163" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E163" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F163" s="25" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G163" s="25" t="n">
-        <v>1</v>
+      <c r="A163" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D163" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E163" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F163" s="23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="164">
@@ -7192,7 +7196,7 @@
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1435</t>
+          <t>US-OR-UNI-UCO-1450</t>
         </is>
       </c>
       <c r="C164" s="24" t="inlineStr">
@@ -7212,46 +7216,46 @@
       </c>
       <c r="F164" s="23" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G164" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="23" t="inlineStr">
+      <c r="A165" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B165" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C165" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D165" s="24" t="inlineStr">
+      <c r="B165" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1421</t>
+        </is>
+      </c>
+      <c r="C165" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D165" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E165" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F165" s="23" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G165" s="23" t="n">
-        <v>1</v>
+      <c r="E165" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F165" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G165" s="25" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="166">
@@ -7262,7 +7266,7 @@
       </c>
       <c r="B166" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-UNI-UCO-1436</t>
         </is>
       </c>
       <c r="C166" s="26" t="inlineStr">
@@ -7286,7 +7290,7 @@
         </is>
       </c>
       <c r="G166" s="25" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167">
@@ -7297,7 +7301,7 @@
       </c>
       <c r="B167" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C167" s="26" t="inlineStr">
@@ -7332,7 +7336,7 @@
       </c>
       <c r="B168" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C168" s="26" t="inlineStr">
@@ -7352,7 +7356,7 @@
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G168" s="25" t="n">
@@ -7360,73 +7364,73 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B169" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1438</t>
-        </is>
-      </c>
-      <c r="C169" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D169" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E169" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F169" s="25" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G169" s="25" t="n">
-        <v>9</v>
+      <c r="A169" s="23" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B169" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C169" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D169" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E169" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F169" s="23" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="23" t="inlineStr">
+      <c r="A170" s="25" t="inlineStr">
         <is>
           <t>97603</t>
         </is>
       </c>
-      <c r="B170" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C170" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D170" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E170" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F170" s="23" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G170" s="23" t="n">
-        <v>15</v>
+      <c r="B170" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C170" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D170" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E170" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F170" s="25" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G170" s="25" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="171">
@@ -7437,7 +7441,7 @@
       </c>
       <c r="B171" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1936</t>
         </is>
       </c>
       <c r="C171" s="26" t="inlineStr">
@@ -7457,11 +7461,11 @@
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G171" s="25" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -7472,7 +7476,7 @@
       </c>
       <c r="B172" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1936</t>
+          <t>US-OR-KLA-KLA-2256</t>
         </is>
       </c>
       <c r="C172" s="26" t="inlineStr">
@@ -7492,11 +7496,11 @@
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G172" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -7507,7 +7511,7 @@
       </c>
       <c r="B173" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2256</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C173" s="26" t="inlineStr">
@@ -7527,7 +7531,7 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G173" s="25" t="n">
@@ -7542,7 +7546,7 @@
       </c>
       <c r="B174" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1931</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C174" s="26" t="inlineStr">
@@ -7562,7 +7566,7 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G174" s="25" t="n">
@@ -7570,38 +7574,38 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B175" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1701</t>
-        </is>
-      </c>
-      <c r="C175" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D175" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E175" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F175" s="25" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G175" s="25" t="n">
-        <v>1</v>
+      <c r="A175" s="23" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B175" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C175" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D175" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E175" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F175" s="23" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -7612,7 +7616,7 @@
       </c>
       <c r="B176" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-039</t>
+          <t>US-OR-UMA-UMC-121-B</t>
         </is>
       </c>
       <c r="C176" s="24" t="inlineStr">
@@ -7632,46 +7636,46 @@
       </c>
       <c r="F176" s="23" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G176" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="23" t="inlineStr">
+      <c r="A177" s="25" t="inlineStr">
         <is>
           <t>97862</t>
         </is>
       </c>
-      <c r="B177" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C177" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D177" s="24" t="inlineStr">
+      <c r="B177" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C177" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D177" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E177" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F177" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G177" s="23" t="n">
-        <v>1</v>
+      <c r="E177" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F177" s="25" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G177" s="25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="178">
@@ -7682,7 +7686,7 @@
       </c>
       <c r="B178" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-032</t>
+          <t>US-OR-UMA-UMC-123-B</t>
         </is>
       </c>
       <c r="C178" s="26" t="inlineStr">
@@ -7702,11 +7706,11 @@
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="G178" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -7717,7 +7721,7 @@
       </c>
       <c r="B179" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>US-OR-UMA-UMC-1406025-B</t>
         </is>
       </c>
       <c r="C179" s="26" t="inlineStr">
@@ -7737,7 +7741,7 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G179" s="25" t="n">
@@ -7745,73 +7749,73 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="25" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B180" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
-        </is>
-      </c>
-      <c r="C180" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D180" s="26" t="inlineStr">
+      <c r="A180" s="23" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B180" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C180" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D180" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E180" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F180" s="25" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G180" s="25" t="n">
+      <c r="E180" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F180" s="23" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G180" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="23" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B181" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C181" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D181" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E181" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F181" s="23" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G181" s="23" t="n">
-        <v>1</v>
+      <c r="A181" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B181" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-8SB</t>
+        </is>
+      </c>
+      <c r="C181" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D181" s="26" t="inlineStr">
+        <is>
+          <t>Crook</t>
+        </is>
+      </c>
+      <c r="E181" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F181" s="25" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="G181" s="25" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="182">
@@ -7822,7 +7826,7 @@
       </c>
       <c r="B182" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SB</t>
+          <t>US-OR-CRO-CRR-4SC</t>
         </is>
       </c>
       <c r="C182" s="26" t="inlineStr">
@@ -7842,11 +7846,11 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G182" s="25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183">
@@ -7857,7 +7861,7 @@
       </c>
       <c r="B183" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC</t>
+          <t>US-OR-CRO-CRR-4SK-A</t>
         </is>
       </c>
       <c r="C183" s="26" t="inlineStr">
@@ -7881,28 +7885,28 @@
         </is>
       </c>
       <c r="G183" s="25" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B184" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-A</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C184" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D184" s="26" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E184" s="25" t="inlineStr">
@@ -7912,32 +7916,32 @@
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="G184" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="25" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B185" s="26" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C185" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D185" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E185" s="25" t="inlineStr">
@@ -7947,11 +7951,11 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G185" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -7962,7 +7966,7 @@
       </c>
       <c r="B186" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C186" s="26" t="inlineStr">
@@ -7982,32 +7986,32 @@
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G186" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B187" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C187" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D187" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E187" s="25" t="inlineStr">
@@ -8017,22 +8021,22 @@
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G187" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="25" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B188" s="26" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C188" s="26" t="inlineStr">
@@ -8042,7 +8046,7 @@
       </c>
       <c r="D188" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E188" s="25" t="inlineStr">
@@ -8052,32 +8056,32 @@
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G188" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="25" t="inlineStr">
         <is>
-          <t>97028</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B189" s="26" t="inlineStr">
         <is>
-          <t>White River</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C189" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D189" s="26" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E189" s="25" t="inlineStr">
@@ -8094,43 +8098,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="25" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B190" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C190" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D190" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E190" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F190" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G190" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" s="27" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -8138,7 +8107,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A192:G192"/>
+    <mergeCell ref="A191:G191"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
